--- a/data/trans_dic/P59A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 23,04</t>
+          <t>8,97; 23,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 29,59</t>
+          <t>15,27; 30,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,09; 30,68</t>
+          <t>15,49; 31,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 26,22</t>
+          <t>11,03; 26,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 17,92</t>
+          <t>6,05; 19,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,77; 32,84</t>
+          <t>14,93; 32,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,28; 34,59</t>
+          <t>19,32; 35,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 26,54</t>
+          <t>12,14; 26,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,13; 17,97</t>
+          <t>9,34; 18,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,28; 28,32</t>
+          <t>16,69; 28,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,08; 30,23</t>
+          <t>19,78; 30,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,77; 23,52</t>
+          <t>13,7; 23,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 18,08</t>
+          <t>7,17; 17,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 21,23</t>
+          <t>10,53; 21,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 16,65</t>
+          <t>6,82; 16,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 25,1</t>
+          <t>12,01; 25,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 14,87</t>
+          <t>6,12; 15,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,74</t>
+          <t>8,6; 18,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 12,77</t>
+          <t>4,77; 12,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,26; 25,4</t>
+          <t>15,44; 25,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 14,12</t>
+          <t>7,64; 14,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,11; 18,78</t>
+          <t>11,12; 18,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,09</t>
+          <t>6,81; 12,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,05; 23,85</t>
+          <t>14,91; 23,23</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 23,23</t>
+          <t>9,92; 24,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 16,77</t>
+          <t>6,23; 17,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 21,62</t>
+          <t>9,35; 22,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 17,55</t>
+          <t>7,3; 17,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 15,49</t>
+          <t>5,11; 14,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 16,39</t>
+          <t>4,64; 17,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 15,15</t>
+          <t>5,16; 14,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 18,11</t>
+          <t>9,66; 18,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 16,5</t>
+          <t>8,34; 16,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 15,05</t>
+          <t>6,83; 13,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 15,54</t>
+          <t>7,93; 16,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 16,62</t>
+          <t>9,54; 16,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 21,66</t>
+          <t>9,97; 22,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,53; 30,26</t>
+          <t>15,24; 29,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 43,0</t>
+          <t>27,21; 43,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,41; 35,94</t>
+          <t>17,8; 36,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 20,16</t>
+          <t>8,95; 18,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 25,43</t>
+          <t>12,28; 25,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,09; 33,67</t>
+          <t>20,05; 33,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 19,53</t>
+          <t>5,9; 19,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,1; 18,91</t>
+          <t>10,53; 18,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,15; 24,76</t>
+          <t>15,0; 25,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,16; 36,16</t>
+          <t>25,96; 36,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,34; 24,11</t>
+          <t>10,65; 24,06</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 24,62</t>
+          <t>9,54; 24,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 21,59</t>
+          <t>5,88; 21,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 19,05</t>
+          <t>4,4; 19,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 16,99</t>
+          <t>4,47; 17,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 24,05</t>
+          <t>7,6; 24,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 25,55</t>
+          <t>9,34; 25,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 15,41</t>
+          <t>3,68; 16,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,23</t>
+          <t>6,69; 16,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 21,57</t>
+          <t>10,72; 21,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 20,76</t>
+          <t>9,23; 20,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 14,89</t>
+          <t>5,61; 15,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,76</t>
+          <t>6,73; 14,89</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,26; 25,64</t>
+          <t>10,28; 25,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 19,98</t>
+          <t>5,7; 21,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 13,73</t>
+          <t>2,84; 13,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,61; 18,16</t>
+          <t>7,34; 17,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 19,75</t>
+          <t>7,53; 19,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 12,55</t>
+          <t>2,29; 11,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 11,8</t>
+          <t>2,6; 11,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,17; 19,29</t>
+          <t>8,64; 19,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,42; 20,07</t>
+          <t>10,44; 20,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 13,58</t>
+          <t>5,13; 13,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,68</t>
+          <t>3,93; 10,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,33; 17,07</t>
+          <t>9,33; 16,75</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,71; 18,91</t>
+          <t>9,99; 19,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,79; 22,46</t>
+          <t>12,01; 22,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,96; 22,69</t>
+          <t>13,79; 22,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,48; 21,78</t>
+          <t>11,65; 21,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 13,03</t>
+          <t>5,73; 13,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,95; 23,43</t>
+          <t>13,42; 22,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,32; 16,68</t>
+          <t>9,22; 16,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,08; 19,79</t>
+          <t>12,09; 19,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,83; 14,92</t>
+          <t>8,72; 14,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,35; 21,01</t>
+          <t>14,09; 21,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,58; 18,08</t>
+          <t>12,48; 18,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,01; 19,68</t>
+          <t>12,92; 19,27</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,7</t>
+          <t>7,46; 14,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,4; 16,61</t>
+          <t>8,16; 16,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,14; 19,9</t>
+          <t>11,85; 20,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,0; 17,32</t>
+          <t>8,73; 17,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,34</t>
+          <t>5,03; 11,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,99; 15,41</t>
+          <t>7,79; 15,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,79; 17,73</t>
+          <t>10,53; 17,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,61</t>
+          <t>2,51; 6,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,68</t>
+          <t>6,74; 11,73</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,91; 14,62</t>
+          <t>9,07; 14,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,3; 18,04</t>
+          <t>12,44; 17,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 10,4</t>
+          <t>5,98; 10,32</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,88</t>
+          <t>11,83; 15,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,77</t>
+          <t>13,4; 17,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,55; 19,57</t>
+          <t>15,53; 19,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,79; 18,11</t>
+          <t>13,73; 18,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,87</t>
+          <t>8,57; 12,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,44; 16,12</t>
+          <t>12,4; 16,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,43; 15,92</t>
+          <t>12,37; 16,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,93</t>
+          <t>11,15; 14,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,55; 13,19</t>
+          <t>10,65; 13,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13,34; 16,13</t>
+          <t>13,39; 16,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14,36; 17,06</t>
+          <t>14,45; 17,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,02; 16,07</t>
+          <t>13,01; 15,87</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10681; 26482</t>
+          <t>10308; 26901</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18178; 38411</t>
+          <t>19823; 39506</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18908; 38441</t>
+          <t>19412; 39642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18854; 43066</t>
+          <t>18124; 43868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6812; 21519</t>
+          <t>7260; 22860</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16565; 36849</t>
+          <t>16753; 36060</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27209; 48812</t>
+          <t>27268; 49671</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16431; 35415</t>
+          <t>16203; 35917</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21447; 42224</t>
+          <t>21939; 44199</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41830; 68528</t>
+          <t>40397; 68042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50814; 80539</t>
+          <t>52686; 81942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40994; 70019</t>
+          <t>40775; 69557</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12835; 33991</t>
+          <t>13469; 33646</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20157; 40769</t>
+          <t>20225; 41322</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14146; 33836</t>
+          <t>13871; 33014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36126; 70774</t>
+          <t>33855; 70555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11829; 29261</t>
+          <t>12046; 29851</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17686; 37070</t>
+          <t>17005; 37556</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9847; 26276</t>
+          <t>9810; 25037</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38464; 64002</t>
+          <t>38920; 64278</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28293; 54335</t>
+          <t>29408; 56769</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43319; 73201</t>
+          <t>43360; 72888</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27719; 53561</t>
+          <t>27875; 52357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80346; 127333</t>
+          <t>79593; 124066</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11460; 26952</t>
+          <t>11515; 28075</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9367; 23190</t>
+          <t>8622; 23613</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9951; 24587</t>
+          <t>10631; 26137</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11862; 28482</t>
+          <t>11856; 28350</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6908; 21423</t>
+          <t>7074; 20277</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6740; 22988</t>
+          <t>6507; 24739</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7878; 22557</t>
+          <t>7683; 22199</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17844; 34511</t>
+          <t>18415; 35406</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22092; 41970</t>
+          <t>21213; 42315</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19856; 41937</t>
+          <t>19038; 38729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20981; 40829</t>
+          <t>20819; 42671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34760; 58660</t>
+          <t>33681; 57770</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13442; 30813</t>
+          <t>14176; 31667</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24022; 46809</t>
+          <t>23578; 46230</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46432; 71245</t>
+          <t>45080; 71425</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30343; 62630</t>
+          <t>31025; 63112</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15365; 34614</t>
+          <t>15366; 32476</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18794; 38302</t>
+          <t>18504; 38000</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35663; 59774</t>
+          <t>35600; 59101</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13819; 52563</t>
+          <t>15880; 53756</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34837; 59372</t>
+          <t>33066; 58305</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46265; 75601</t>
+          <t>45790; 77423</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89787; 124115</t>
+          <t>89109; 125179</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45869; 106925</t>
+          <t>47213; 106700</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9597; 23368</t>
+          <t>9057; 23432</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4511; 18298</t>
+          <t>4982; 18100</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4199; 16284</t>
+          <t>3762; 16271</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3776; 14685</t>
+          <t>3866; 14836</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7057; 19650</t>
+          <t>6205; 19838</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8489; 23459</t>
+          <t>8573; 23232</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1986; 10815</t>
+          <t>2586; 11233</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5431; 14702</t>
+          <t>6056; 14938</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19418; 38106</t>
+          <t>18934; 38254</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16831; 36656</t>
+          <t>16289; 35950</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8687; 23177</t>
+          <t>8733; 23484</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12045; 26119</t>
+          <t>11904; 26349</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11338; 28320</t>
+          <t>11354; 28276</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5171; 20754</t>
+          <t>5923; 22461</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3657; 14352</t>
+          <t>2970; 13842</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10766; 25704</t>
+          <t>10390; 25233</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8944; 23448</t>
+          <t>8938; 23229</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2895; 13207</t>
+          <t>2407; 12144</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2799; 13022</t>
+          <t>2870; 13167</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11041; 26050</t>
+          <t>11668; 26745</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23878; 46002</t>
+          <t>23921; 46588</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10444; 28407</t>
+          <t>10734; 28517</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8478; 22958</t>
+          <t>8456; 22361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25804; 47230</t>
+          <t>25799; 46328</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21413; 41713</t>
+          <t>22024; 42462</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34209; 60078</t>
+          <t>32134; 59688</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44711; 72692</t>
+          <t>44191; 72958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35976; 68238</t>
+          <t>36504; 68318</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13610; 31994</t>
+          <t>14067; 32833</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40225; 67561</t>
+          <t>38690; 66167</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35369; 63298</t>
+          <t>34977; 60960</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>39382; 64517</t>
+          <t>39398; 64871</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41144; 69552</t>
+          <t>40655; 67754</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79751; 116802</t>
+          <t>78331; 118385</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88015; 126567</t>
+          <t>87369; 126113</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>83196; 125820</t>
+          <t>82611; 123167</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22325; 44253</t>
+          <t>22469; 44573</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26254; 51877</t>
+          <t>25478; 51264</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41700; 68374</t>
+          <t>40706; 69342</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27496; 52904</t>
+          <t>26680; 52426</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14548; 35098</t>
+          <t>15562; 34185</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26947; 51989</t>
+          <t>26282; 51127</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38810; 63758</t>
+          <t>37871; 63917</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8411; 23491</t>
+          <t>8917; 22985</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42495; 71330</t>
+          <t>41148; 71597</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>57872; 95032</t>
+          <t>58910; 91708</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>86506; 126860</t>
+          <t>87483; 125987</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>38261; 68725</t>
+          <t>39525; 68189</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>151556; 204574</t>
+          <t>152374; 203455</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>187924; 245821</t>
+          <t>185313; 241494</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>227296; 286069</t>
+          <t>227067; 287809</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>224744; 295040</t>
+          <t>223772; 297705</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>118904; 164076</t>
+          <t>118514; 167653</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>177179; 229468</t>
+          <t>176522; 230592</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>197988; 253637</t>
+          <t>197057; 255272</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>193613; 261573</t>
+          <t>195437; 260487</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>281649; 352236</t>
+          <t>284463; 353780</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>374364; 452819</t>
+          <t>375886; 456788</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>438777; 521238</t>
+          <t>441393; 522749</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>440373; 543579</t>
+          <t>439869; 536616</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P59A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 23,4</t>
+          <t>9,23; 22,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,27; 30,43</t>
+          <t>15,43; 30,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 31,64</t>
+          <t>15,03; 31,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,03; 26,7</t>
+          <t>12,61; 25,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 19,04</t>
+          <t>5,96; 18,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,93; 32,14</t>
+          <t>14,58; 32,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,32; 35,2</t>
+          <t>19,5; 34,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 26,91</t>
+          <t>12,61; 24,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,34; 18,81</t>
+          <t>9,1; 17,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,69; 28,12</t>
+          <t>17,44; 28,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,78; 30,76</t>
+          <t>19,31; 30,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,7; 23,36</t>
+          <t>13,77; 22,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 17,9</t>
+          <t>6,96; 17,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 21,52</t>
+          <t>10,45; 20,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 16,24</t>
+          <t>6,68; 16,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 25,02</t>
+          <t>13,71; 26,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 15,17</t>
+          <t>6,07; 14,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 18,99</t>
+          <t>9,13; 19,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 12,16</t>
+          <t>4,89; 12,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,44; 25,5</t>
+          <t>14,94; 24,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 14,75</t>
+          <t>7,6; 14,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,12; 18,7</t>
+          <t>11,49; 18,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,8</t>
+          <t>7,0; 13,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,91; 23,23</t>
+          <t>15,12; 23,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 24,2</t>
+          <t>10,13; 23,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 17,07</t>
+          <t>6,37; 17,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 22,98</t>
+          <t>9,01; 22,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 17,47</t>
+          <t>8,87; 19,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 14,66</t>
+          <t>5,0; 14,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 17,64</t>
+          <t>4,73; 16,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 14,91</t>
+          <t>5,2; 14,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 18,58</t>
+          <t>9,64; 18,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,64</t>
+          <t>8,36; 16,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 13,9</t>
+          <t>6,79; 14,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,24</t>
+          <t>7,82; 16,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 16,37</t>
+          <t>10,35; 17,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 22,26</t>
+          <t>10,33; 22,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,24; 29,89</t>
+          <t>15,71; 30,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,21; 43,11</t>
+          <t>28,18; 43,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 36,21</t>
+          <t>16,59; 34,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 18,91</t>
+          <t>8,66; 19,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,28; 25,23</t>
+          <t>12,2; 24,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 33,29</t>
+          <t>20,37; 33,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 19,97</t>
+          <t>12,71; 23,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,53; 18,57</t>
+          <t>10,45; 18,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 25,36</t>
+          <t>15,41; 24,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,96; 36,47</t>
+          <t>25,91; 36,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 24,06</t>
+          <t>16,3; 27,47</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 24,68</t>
+          <t>10,02; 25,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 21,36</t>
+          <t>5,25; 22,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 19,03</t>
+          <t>4,74; 19,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 17,17</t>
+          <t>4,37; 17,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 24,28</t>
+          <t>7,92; 25,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 25,3</t>
+          <t>9,77; 24,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 16,0</t>
+          <t>2,77; 15,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,69; 16,49</t>
+          <t>7,03; 17,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,72; 21,66</t>
+          <t>10,49; 21,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 20,36</t>
+          <t>9,4; 20,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 15,08</t>
+          <t>5,44; 15,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,73; 14,89</t>
+          <t>6,71; 14,44</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,28; 25,6</t>
+          <t>10,31; 25,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,7; 21,62</t>
+          <t>5,73; 21,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,84; 13,24</t>
+          <t>3,6; 13,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,34; 17,83</t>
+          <t>7,89; 17,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 19,57</t>
+          <t>7,8; 20,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 11,54</t>
+          <t>2,07; 11,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,93</t>
+          <t>2,47; 10,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 19,8</t>
+          <t>8,82; 19,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,44; 20,33</t>
+          <t>10,69; 20,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,64</t>
+          <t>5,03; 13,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,4</t>
+          <t>3,63; 10,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,33; 16,75</t>
+          <t>9,75; 17,17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,99; 19,25</t>
+          <t>10,01; 19,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,01; 22,31</t>
+          <t>12,84; 21,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,79; 22,77</t>
+          <t>13,95; 23,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,65; 21,8</t>
+          <t>12,5; 22,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,37</t>
+          <t>5,43; 12,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,42; 22,94</t>
+          <t>13,57; 23,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,22; 16,06</t>
+          <t>9,43; 16,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,09; 19,9</t>
+          <t>13,52; 21,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,72; 14,54</t>
+          <t>8,72; 14,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,09; 21,3</t>
+          <t>14,3; 21,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,48; 18,02</t>
+          <t>12,52; 18,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,92; 19,27</t>
+          <t>14,23; 20,4</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 14,8</t>
+          <t>7,61; 15,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,41</t>
+          <t>8,15; 15,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,85; 20,18</t>
+          <t>12,02; 20,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,73; 17,16</t>
+          <t>9,07; 17,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,05</t>
+          <t>4,68; 11,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,79; 15,15</t>
+          <t>7,76; 15,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,53; 17,77</t>
+          <t>10,48; 17,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,47</t>
+          <t>2,53; 6,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,74; 11,73</t>
+          <t>6,81; 11,4</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,07; 14,11</t>
+          <t>8,75; 14,17</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,44; 17,92</t>
+          <t>12,3; 17,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,98; 10,32</t>
+          <t>6,22; 10,76</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,83; 15,79</t>
+          <t>11,82; 15,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,4; 17,46</t>
+          <t>13,31; 17,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,53; 19,69</t>
+          <t>15,46; 19,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,73; 18,27</t>
+          <t>14,24; 18,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,13</t>
+          <t>8,62; 12,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,2</t>
+          <t>12,24; 16,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,37; 16,02</t>
+          <t>12,32; 15,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,15; 14,87</t>
+          <t>12,21; 15,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,65; 13,25</t>
+          <t>10,65; 13,38</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13,39; 16,27</t>
+          <t>13,31; 16,12</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14,45; 17,11</t>
+          <t>14,38; 17,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,01; 15,87</t>
+          <t>13,8; 16,44</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54009</t>
+          <t>53473</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10308; 26901</t>
+          <t>10608; 26112</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19823; 39506</t>
+          <t>20036; 39383</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19412; 39642</t>
+          <t>18832; 38990</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18124; 43868</t>
+          <t>19168; 38982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7260; 22860</t>
+          <t>7153; 21940</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16753; 36060</t>
+          <t>16359; 36153</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27268; 49671</t>
+          <t>27515; 48674</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16203; 35917</t>
+          <t>18573; 35889</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21939; 44199</t>
+          <t>21378; 41981</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40397; 68042</t>
+          <t>42214; 69404</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52686; 81942</t>
+          <t>51434; 81050</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40775; 69557</t>
+          <t>41214; 67432</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50811</t>
+          <t>52248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49895</t>
+          <t>51823</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>100706</t>
+          <t>104071</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13469; 33646</t>
+          <t>13076; 32299</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20225; 41322</t>
+          <t>20064; 40033</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13871; 33014</t>
+          <t>13574; 33553</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33855; 70555</t>
+          <t>37856; 72609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12046; 29851</t>
+          <t>11951; 29457</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17005; 37556</t>
+          <t>18054; 37969</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9810; 25037</t>
+          <t>10064; 25217</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38920; 64278</t>
+          <t>39626; 65165</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29408; 56769</t>
+          <t>29238; 57366</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43360; 72888</t>
+          <t>44777; 73306</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27875; 52357</t>
+          <t>28639; 54251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>79593; 124066</t>
+          <t>81860; 127398</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25690</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>47584</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11515; 28075</t>
+          <t>11752; 27814</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8622; 23613</t>
+          <t>8814; 24070</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10631; 26137</t>
+          <t>10245; 25375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11856; 28350</t>
+          <t>14423; 32462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7074; 20277</t>
+          <t>6913; 20181</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6507; 24739</t>
+          <t>6634; 22937</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7683; 22199</t>
+          <t>7740; 22006</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18415; 35406</t>
+          <t>18485; 35418</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21213; 42315</t>
+          <t>21274; 42080</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19038; 38729</t>
+          <t>18913; 40803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20819; 42671</t>
+          <t>20540; 42248</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33681; 57770</t>
+          <t>36676; 61581</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34666</t>
+          <t>39399</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80071</t>
+          <t>91602</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14176; 31667</t>
+          <t>14698; 32114</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23578; 46230</t>
+          <t>24294; 46974</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45080; 71425</t>
+          <t>46692; 71613</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31025; 63112</t>
+          <t>34528; 70851</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15366; 32476</t>
+          <t>14862; 33520</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18504; 38000</t>
+          <t>18374; 37587</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35600; 59101</t>
+          <t>36159; 59920</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15880; 53756</t>
+          <t>28673; 53794</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33066; 58305</t>
+          <t>32809; 57880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45790; 77423</t>
+          <t>47046; 75571</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89109; 125179</t>
+          <t>88942; 126291</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47213; 106700</t>
+          <t>70675; 119102</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>19825</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9057; 23432</t>
+          <t>9517; 23905</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4982; 18100</t>
+          <t>4449; 18892</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3762; 16271</t>
+          <t>4055; 16503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3866; 14836</t>
+          <t>4352; 17005</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6205; 19838</t>
+          <t>6473; 20941</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8573; 23232</t>
+          <t>8971; 22651</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2586; 11233</t>
+          <t>1947; 10731</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6056; 14938</t>
+          <t>6965; 16929</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18934; 38254</t>
+          <t>18521; 38431</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16289; 35950</t>
+          <t>16595; 36066</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8733; 23484</t>
+          <t>8476; 23832</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11904; 26349</t>
+          <t>13326; 28678</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18308</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35213</t>
+          <t>35812</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11354; 28276</t>
+          <t>11386; 28116</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5923; 22461</t>
+          <t>5950; 22027</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2970; 13842</t>
+          <t>3767; 14408</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10390; 25233</t>
+          <t>10936; 24781</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8938; 23229</t>
+          <t>9260; 24281</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2407; 12144</t>
+          <t>2175; 12090</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2870; 13167</t>
+          <t>2729; 12048</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11668; 26745</t>
+          <t>12120; 26896</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23921; 46588</t>
+          <t>24496; 46078</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10734; 28517</t>
+          <t>10523; 29028</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8456; 22361</t>
+          <t>7793; 22481</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25799; 46328</t>
+          <t>26912; 47374</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>59616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>51691</t>
+          <t>66747</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>102578</t>
+          <t>126363</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22024; 42462</t>
+          <t>22080; 43255</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32134; 59688</t>
+          <t>34342; 58803</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44191; 72958</t>
+          <t>44696; 74830</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36504; 68318</t>
+          <t>43965; 78282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14067; 32833</t>
+          <t>13331; 31269</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38690; 66167</t>
+          <t>39136; 66690</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34977; 60960</t>
+          <t>35803; 61515</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>39398; 64871</t>
+          <t>52770; 83149</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40655; 67754</t>
+          <t>40642; 66665</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78331; 118385</t>
+          <t>79524; 117313</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87369; 126113</t>
+          <t>87619; 126192</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82611; 123167</t>
+          <t>105619; 151407</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37988</t>
+          <t>45997</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52568</t>
+          <t>64155</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22469; 44573</t>
+          <t>22904; 45542</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25478; 51264</t>
+          <t>25464; 49349</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40706; 69342</t>
+          <t>41284; 69041</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26680; 52426</t>
+          <t>32673; 61663</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15562; 34185</t>
+          <t>14478; 34600</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26282; 51127</t>
+          <t>26176; 51007</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37871; 63917</t>
+          <t>37671; 62749</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8917; 22985</t>
+          <t>10487; 28638</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41148; 71597</t>
+          <t>41591; 69575</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>58910; 91708</t>
+          <t>56848; 92064</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>87483; 125987</t>
+          <t>86460; 124415</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>39525; 68189</t>
+          <t>48199; 83388</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>285198</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>228998</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>487504</t>
+          <t>542885</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>152374; 203455</t>
+          <t>152328; 203813</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>185313; 241494</t>
+          <t>184121; 238355</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>227067; 287809</t>
+          <t>226086; 284564</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>223772; 297705</t>
+          <t>249020; 325349</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>118514; 167653</t>
+          <t>119166; 166694</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>176522; 230592</t>
+          <t>174290; 233501</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>197057; 255272</t>
+          <t>196240; 254437</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>195437; 260487</t>
+          <t>228445; 283176</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>284463; 353780</t>
+          <t>284529; 357341</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>375886; 456788</t>
+          <t>373746; 452634</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>441393; 522749</t>
+          <t>439242; 521488</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>439869; 536616</t>
+          <t>499586; 595084</t>
         </is>
       </c>
     </row>
